--- a/reference/script_es.xlsx
+++ b/reference/script_es.xlsx
@@ -18089,7 +18089,7 @@
       </c>
       <c r="E725" s="2" t="inlineStr">
         <is>
-          <t>Si no la entiendes, no pasa nada. ¿Vienes con nosotros a la Santa Sede?</t>
+          <t>Si no la entiende, no pasa nada. ¿Viene con nosotros a la Santa Sede?</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="E810" s="2" t="inlineStr">
         <is>
-          <t>¡Por eso odio a los de tipo cáscara de bestia!</t>
+          <t>¡Por eso odio a los de tipo cáscara!</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
       </c>
       <c r="E900" s="2" t="inlineStr">
         <is>
-          <t>Anya, espéranos aquí, ¿sí?</t>
+          <t>Anya, espérenos aquí, ¿sí?</t>
         </is>
       </c>
     </row>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="E922" s="2" t="inlineStr">
         <is>
-          <t>disponer así de la gente de la comandante Luna...</t>
+          <t>disponer así de la gente de la comandante Lunaria...</t>
         </is>
       </c>
     </row>
@@ -26093,7 +26093,7 @@
       </c>
       <c r="E1053" s="2" t="inlineStr">
         <is>
-          <t>Anya, ¿estás bien?</t>
+          <t>Señorita Anya, ¿está bien?</t>
         </is>
       </c>
     </row>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="E1059" s="2" t="inlineStr">
         <is>
-          <t>Tranquila, estamos aquí contigo.</t>
+          <t>Tranquila, aquí estamos con usted.</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="E1068" s="2" t="inlineStr">
         <is>
-          <t>Anya, ¿qué te pasa?</t>
+          <t>Señorita Anya, ¿qué le pasa?</t>
         </is>
       </c>
     </row>
@@ -36043,7 +36043,7 @@
       </c>
       <c r="E1459" s="2" t="inlineStr">
         <is>
-          <t>Anya, ¿tienes frío?</t>
+          <t>Anya, ¿tiene frío?</t>
         </is>
       </c>
     </row>
@@ -46660,7 +46660,7 @@
       </c>
       <c r="E1892" s="2" t="inlineStr">
         <is>
-          <t>¿Eh? ¿Anya también sabe?</t>
+          <t>¿Eh? ¿Usted también sabe montar, Anya?</t>
         </is>
       </c>
     </row>
@@ -64422,7 +64422,7 @@
       </c>
       <c r="E2646" s="2" t="inlineStr">
         <is>
-          <t>Sí. Estaremos contigo.</t>
+          <t>Sí. Estaremos con usted.</t>
         </is>
       </c>
     </row>
@@ -70676,7 +70676,7 @@
       </c>
       <c r="E2900" s="2" t="inlineStr">
         <is>
-          <t>¡Son... son cáscaras de bestia!</t>
+          <t>¡Son... son cáscaras!</t>
         </is>
       </c>
     </row>
